--- a/tests/integration_workspace/review_classification_full/output/price_match.xlsx
+++ b/tests/integration_workspace/review_classification_full/output/price_match.xlsx
@@ -494,7 +494,11 @@
           <t>SKU-APPLE</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SVO shampoo apple 1 l</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>A-100</t>
@@ -524,7 +528,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-08-05T18:57:07.023915+00:00</t>
+          <t>2026-08-06T16:38:45.861139+00:00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -570,7 +574,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-08-05T18:57:07.023915+00:00</t>
+          <t>2026-08-06T16:38:45.861139+00:00</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -616,7 +620,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-08-05T18:57:07.023915+00:00</t>
+          <t>2026-08-06T16:38:45.861139+00:00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">

--- a/tests/integration_workspace/review_classification_full/output/price_match.xlsx
+++ b/tests/integration_workspace/review_classification_full/output/price_match.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-08-06T16:38:45.861139+00:00</t>
+          <t>2026-09-03T09:09:03.099507+00:00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-08-06T16:38:45.861139+00:00</t>
+          <t>2026-09-03T09:09:03.099507+00:00</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-08-06T16:38:45.861139+00:00</t>
+          <t>2026-09-03T09:09:03.099507+00:00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
